--- a/artfynd/S 902-2024 artfynd.xlsx
+++ b/artfynd/S 902-2024 artfynd.xlsx
@@ -1352,7 +1352,7 @@
         <v>136152858</v>
       </c>
       <c r="B8" t="n">
-        <v>80594</v>
+        <v>80596</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1469,7 +1469,7 @@
         <v>136152860</v>
       </c>
       <c r="B9" t="n">
-        <v>80594</v>
+        <v>80596</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/S 902-2024 artfynd.xlsx
+++ b/artfynd/S 902-2024 artfynd.xlsx
@@ -2002,29 +2002,29 @@
         <v>112431163</v>
       </c>
       <c r="B14" t="n">
-        <v>89018</v>
+        <v>89206</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>797</v>
+        <v>802</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lilavaxing</t>
+          <t>Grålila vaxing</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cuphophyllus flavipes</t>
+          <t>Cuphophyllus lacmus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Britzelm.) Bon</t>
+          <t>(Schumach.) Bon</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>

--- a/artfynd/S 902-2024 artfynd.xlsx
+++ b/artfynd/S 902-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ25"/>
+  <dimension ref="A1:AZ26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>6195331</v>
+        <v>136950525</v>
       </c>
       <c r="B2" t="n">
-        <v>97990</v>
+        <v>99355</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,33 +691,45 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>224358</v>
+        <v>219811</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig plattlummer</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum subsp. complanatum</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Skogsbilväg N om Korstabodarna, Jmt</t>
+          <t>Kallsta, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488603</v>
+        <v>482459</v>
       </c>
       <c r="R2" t="n">
-        <v>7026481</v>
+        <v>7031512</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -741,12 +753,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2002-07-15</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2002-07-15</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -755,78 +767,69 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Artificiell miljö</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Vägkant</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Staffan Åström</t>
+          <t>Staffan Fridh</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Staffan Åström</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Signe Jönsson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
+        </is>
+      </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/6195331</t>
+          <t>https://artportalen.se/Sighting/136950525</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112076813</v>
+        <v>6195331</v>
       </c>
       <c r="B3" t="n">
-        <v>91909</v>
+        <v>97990</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>224358</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vanlig plattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Lycopodium complanatum subsp. complanatum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>spikbodarna, Jmt</t>
+          <t>Skogsbilväg N om Korstabodarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>485751</v>
+        <v>488603</v>
       </c>
       <c r="R3" t="n">
-        <v>7005707</v>
+        <v>7026481</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -848,17 +851,17 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Östersund</t>
+          <t>Lit</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2002-07-15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2002-07-15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -869,31 +872,41 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Artificiell miljö</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Staffan Åström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Staffan Åström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112076813</t>
+          <t>https://artportalen.se/Sighting/6195331</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112076818</v>
+        <v>112076813</v>
       </c>
       <c r="B4" t="n">
-        <v>91361</v>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -901,21 +914,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3286</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Flattoppad klubbsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Clavariadelphus truncatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Quél.) Donk</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -925,10 +938,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>485662</v>
+        <v>485751</v>
       </c>
       <c r="R4" t="n">
-        <v>7005637</v>
+        <v>7005707</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,13 +999,13 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112076818</t>
+          <t>https://artportalen.se/Sighting/112076813</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128654619</v>
+        <v>112076818</v>
       </c>
       <c r="B5" t="n">
         <v>91361</v>
@@ -1020,31 +1033,20 @@
           <t>(Quél.) Donk</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Spikbodarna, Östersund, Jmt</t>
+          <t>spikbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>485635</v>
+        <v>485662</v>
       </c>
       <c r="R5" t="n">
-        <v>7005628</v>
+        <v>7005637</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1068,12 +1070,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1082,34 +1084,33 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Christer Pålsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Christer Pålsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128654619</t>
+          <t>https://artportalen.se/Sighting/112076818</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112076812</v>
+        <v>128654619</v>
       </c>
       <c r="B6" t="n">
-        <v>89156</v>
+        <v>91361</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1117,37 +1118,48 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4412</v>
+        <v>3286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Flattoppad klubbsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Clavariadelphus truncatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Quél.) Donk</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>spikbodarna, Jmt</t>
+          <t>Spikbodarna, Östersund, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>485781</v>
+        <v>485635</v>
       </c>
       <c r="R6" t="n">
-        <v>7005720</v>
+        <v>7005628</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1171,12 +1183,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1185,74 +1197,72 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Christer Pålsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Christer Pålsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112076812</t>
+          <t>https://artportalen.se/Sighting/128654619</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113057263</v>
+        <v>112076812</v>
       </c>
       <c r="B7" t="n">
-        <v>79327</v>
+        <v>89156</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>4412</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Sacc. &amp; Cub.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Spikbodarna, Jmt</t>
+          <t>spikbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>485704</v>
+        <v>485781</v>
       </c>
       <c r="R7" t="n">
-        <v>7005674</v>
+        <v>7005720</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1276,17 +1286,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-10-31</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-10-31</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Relativt långväxta bålar av garnlav på gran. Obs! Fyndplatsen ligger inom ett avverkningsanmält skogsbestånd med beteckning A 32699-2023.</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1295,102 +1300,74 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Grandominerad, flerskiktad och luckig äldre skog med fältskikt dominerat av blåbärs- och lingonris och med inslag av örter och gräs. Förekomst av måttliga mängder stående och liggande död ved. Flertalet större myrstackar finns i skogsbeståndet. På frisk och frisk-fuktig mark.</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Torra döda grenar på granens nedre del av stammen. # Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113057263</t>
+          <t>https://artportalen.se/Sighting/112076812</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>136152858</v>
+        <v>113057263</v>
       </c>
       <c r="B8" t="n">
-        <v>80596</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Spikbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>485743</v>
+        <v>485704</v>
       </c>
       <c r="R8" t="n">
-        <v>7005475</v>
+        <v>7005674</v>
       </c>
       <c r="S8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1414,27 +1391,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>10:47</t>
+          <t>2023-10-31</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>10:47</t>
+          <t>2023-10-31</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På sälg</t>
+          <t>Relativt långväxta bålar av garnlav på gran. Obs! Fyndplatsen ligger inom ett avverkningsanmält skogsbestånd med beteckning A 32699-2023.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1443,30 +1410,61 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Grandominerad, flerskiktad och luckig äldre skog med fältskikt dominerat av blåbärs- och lingonris och med inslag av örter och gräs. Förekomst av måttliga mängder stående och liggande död ved. Flertalet större myrstackar finns i skogsbeståndet. På frisk och frisk-fuktig mark.</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Torra döda grenar på granens nedre del av stammen. # Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Ingo Strassmann</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Ingo Strassmann</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136152858</t>
+          <t>https://artportalen.se/Sighting/113057263</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>136152860</v>
+        <v>136152858</v>
       </c>
       <c r="B9" t="n">
         <v>80596</v>
@@ -1501,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>485591</v>
+        <v>485743</v>
       </c>
       <c r="R9" t="n">
-        <v>7005590</v>
+        <v>7005475</v>
       </c>
       <c r="S9" t="n">
         <v>2</v>
@@ -1536,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1546,7 +1544,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:47</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På sälg</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1572,54 +1575,54 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136152860</t>
+          <t>https://artportalen.se/Sighting/136152858</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>112076815</v>
+        <v>136152860</v>
       </c>
       <c r="B10" t="n">
-        <v>99118</v>
+        <v>80596</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>spikbodarna, Jmt</t>
+          <t>Spikbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>485636</v>
+        <v>485591</v>
       </c>
       <c r="R10" t="n">
-        <v>7005629</v>
+        <v>7005590</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1643,12 +1646,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-09-12</t>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1663,24 +1676,24 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Ingo Strassmann</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Ingo Strassmann</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112076815</t>
+          <t>https://artportalen.se/Sighting/136152860</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>112076816</v>
+        <v>112076815</v>
       </c>
       <c r="B11" t="n">
         <v>99118</v>
@@ -1715,10 +1728,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>485618</v>
+        <v>485636</v>
       </c>
       <c r="R11" t="n">
-        <v>7005614</v>
+        <v>7005629</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1776,13 +1789,13 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112076816</t>
+          <t>https://artportalen.se/Sighting/112076815</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>112076817</v>
+        <v>112076816</v>
       </c>
       <c r="B12" t="n">
         <v>99118</v>
@@ -1817,10 +1830,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>485596</v>
+        <v>485618</v>
       </c>
       <c r="R12" t="n">
-        <v>7005613</v>
+        <v>7005614</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1878,13 +1891,13 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112076817</t>
+          <t>https://artportalen.se/Sighting/112076816</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128654616</v>
+        <v>112076817</v>
       </c>
       <c r="B13" t="n">
         <v>99118</v>
@@ -1912,32 +1925,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Spikbodarna, Östersund, Jmt</t>
+          <t>spikbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>485635</v>
+        <v>485596</v>
       </c>
       <c r="R13" t="n">
-        <v>7005628</v>
+        <v>7005613</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1961,12 +1962,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1975,34 +1976,33 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Christer Pålsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Christer Pålsson</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128654616</t>
+          <t>https://artportalen.se/Sighting/112076817</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>112431163</v>
+        <v>128654616</v>
       </c>
       <c r="B14" t="n">
-        <v>89206</v>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2010,37 +2010,46 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>802</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Grålila vaxing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cuphophyllus lacmus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schumach.) Bon</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Kraftledningsgata norr om Småbodarna, Jmt</t>
+          <t>Spikbodarna, Östersund, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>485894</v>
+        <v>485635</v>
       </c>
       <c r="R14" t="n">
-        <v>7005070</v>
+        <v>7005628</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2067,12 +2076,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-09-30</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-09-30</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2088,49 +2097,49 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Christer Pålsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Christer Pålsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112431163</t>
+          <t>https://artportalen.se/Sighting/128654616</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>112422051</v>
+        <v>112431163</v>
       </c>
       <c r="B15" t="n">
-        <v>89092</v>
+        <v>89206</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2017</v>
+        <v>802</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Slemvaxing</t>
+          <t>Grålila vaxing</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hygrocybe glutinipes</t>
+          <t>Cuphophyllus lacmus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(J.E.Lange) R.Haller Aar.</t>
+          <t>(Schumach.) Bon</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2205,16 +2214,16 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112422051</t>
+          <t>https://artportalen.se/Sighting/112431163</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>112431067</v>
+        <v>112422051</v>
       </c>
       <c r="B16" t="n">
-        <v>89081</v>
+        <v>89092</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2222,21 +2231,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4374</v>
+        <v>2017</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gulvaxing</t>
+          <t>Slemvaxing</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hygrocybe chlorophana</t>
+          <t>Hygrocybe glutinipes</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Wünsche</t>
+          <t>(J.E.Lange) R.Haller Aar.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2311,54 +2320,57 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112431067</t>
+          <t>https://artportalen.se/Sighting/112422051</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>117485775</v>
+        <v>112431067</v>
       </c>
       <c r="B17" t="n">
-        <v>43249</v>
+        <v>89081</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>101248</v>
+        <v>4374</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Violett guldvinge</t>
+          <t>Gulvaxing</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycaena helle</t>
+          <t>Hygrocybe chlorophana</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
+          <t>(Fr.) Wünsche</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Kraftledningsgata mellan Småbodarna och Mårtensbodarna, Jmt</t>
+          <t>Kraftledningsgata norr om Småbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>485862</v>
+        <v>485894</v>
       </c>
       <c r="R17" t="n">
-        <v>7005052</v>
+        <v>7005070</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2382,22 +2394,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-06-02</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>16:26</t>
+          <t>2023-09-30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-06-02</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>16:26</t>
+          <t>2023-09-30</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2406,6 +2408,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2423,16 +2426,16 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117485775</t>
+          <t>https://artportalen.se/Sighting/112431067</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>111724737</v>
+        <v>117485775</v>
       </c>
       <c r="B18" t="n">
-        <v>106414</v>
+        <v>43249</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2440,34 +2443,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221447</v>
+        <v>101248</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fältgentiana</t>
+          <t>Violett guldvinge</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Gentianella campestris subsp. campestris</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr"/>
+          <t>Lycaena helle</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Kraftlefningsgata mellan Småbodarna och Mårtensbodarna, Jmt</t>
+          <t>Kraftledningsgata mellan Småbodarna och Mårtensbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>485814</v>
+        <v>485862</v>
       </c>
       <c r="R18" t="n">
-        <v>7005042</v>
+        <v>7005052</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2491,12 +2497,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2023-08-27</t>
+          <t>2024-06-02</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2023-08-27</t>
+          <t>2024-06-02</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>16:26</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2522,16 +2538,16 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111724737</t>
+          <t>https://artportalen.se/Sighting/117485775</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>220705</v>
+        <v>111724737</v>
       </c>
       <c r="B19" t="n">
-        <v>106415</v>
+        <v>106414</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2539,37 +2555,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>698</v>
+        <v>221447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sen fältgentiana</t>
+          <t>Fältgentiana</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Gentianella campestris var. campestris</t>
+          <t>Gentianella campestris subsp. campestris</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Småbodarna, Östersund, Jmt</t>
+          <t>Kraftlefningsgata mellan Småbodarna och Mårtensbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>485090</v>
+        <v>485814</v>
       </c>
       <c r="R19" t="n">
-        <v>7004828</v>
+        <v>7005042</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2593,12 +2606,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2003-08-15</t>
+          <t>2023-08-27</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2003-08-15</t>
+          <t>2023-08-27</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2609,36 +2622,31 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>Kraftledningsgata</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Staffan Åström</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Staffan Åström</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/220705</t>
+          <t>https://artportalen.se/Sighting/111724737</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>85978792</v>
+        <v>220705</v>
       </c>
       <c r="B20" t="n">
-        <v>43249</v>
+        <v>106415</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2646,42 +2654,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>101248</v>
+        <v>698</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Violett guldvinge</t>
+          <t>Sen fältgentiana</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycaena helle</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+          <t>Gentianella campestris var. campestris</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Östersund, Jmt</t>
+          <t>Småbodarna, Östersund, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>485091</v>
+        <v>485090</v>
       </c>
       <c r="R20" t="n">
-        <v>7004966</v>
+        <v>7004828</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2705,12 +2708,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2020-06-01</t>
+          <t>2003-08-15</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2020-06-01</t>
+          <t>2003-08-15</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2719,31 +2722,35 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Kraftledningsgata</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Staffan Åström</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Staffan Åström</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/85978792</t>
+          <t>https://artportalen.se/Sighting/220705</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>85978813</v>
+        <v>85978792</v>
       </c>
       <c r="B21" t="n">
         <v>43249</v>
@@ -2771,11 +2778,7 @@
           <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
@@ -2787,10 +2790,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>485096</v>
+        <v>485091</v>
       </c>
       <c r="R21" t="n">
-        <v>7004944</v>
+        <v>7004966</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2849,13 +2852,13 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/85978813</t>
+          <t>https://artportalen.se/Sighting/85978792</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>85978842</v>
+        <v>85978813</v>
       </c>
       <c r="B22" t="n">
         <v>43249</v>
@@ -2899,10 +2902,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>485091</v>
+        <v>485096</v>
       </c>
       <c r="R22" t="n">
-        <v>7004877</v>
+        <v>7004944</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2961,13 +2964,13 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/85978842</t>
+          <t>https://artportalen.se/Sighting/85978813</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>85978872</v>
+        <v>85978842</v>
       </c>
       <c r="B23" t="n">
         <v>43249</v>
@@ -2995,7 +2998,11 @@
           <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
@@ -3007,10 +3014,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>485100</v>
+        <v>485091</v>
       </c>
       <c r="R23" t="n">
-        <v>7004799</v>
+        <v>7004877</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3069,71 +3076,56 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/85978872</t>
+          <t>https://artportalen.se/Sighting/85978842</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>116620214</v>
+        <v>85978872</v>
       </c>
       <c r="B24" t="n">
-        <v>58327</v>
+        <v>43249</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103015</v>
+        <v>101248</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Violett guldvinge</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Lycaena helle</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Spikbodarna, Jmt</t>
+          <t>Östersund, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>485575</v>
+        <v>485100</v>
       </c>
       <c r="R24" t="n">
-        <v>7005187</v>
+        <v>7004799</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3160,12 +3152,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-05-04</t>
+          <t>2020-06-01</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-05-04</t>
+          <t>2020-06-01</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3174,82 +3166,89 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>Grandominerad, flerskiktad och luckig äldre skog med fältskikt dominerat av blåbärs- och lingonris. På frisk-fuktig mark.</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/116620214</t>
+          <t>https://artportalen.se/Sighting/85978872</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>79420805</v>
+        <v>116620214</v>
       </c>
       <c r="B25" t="n">
-        <v>109815</v>
+        <v>58327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220204</v>
+        <v>103015</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Slåtterfibbla</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hypochaeris maculata</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Spikbodarna, 510 m SSV om intill stig, Jmt</t>
+          <t>Spikbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>485178</v>
+        <v>485575</v>
       </c>
       <c r="R25" t="n">
-        <v>7005053</v>
+        <v>7005187</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3276,12 +3275,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2019-08-14</t>
+          <t>2024-05-04</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2019-08-14</t>
+          <t>2024-05-04</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3292,20 +3291,136 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Grandominerad, flerskiktad och luckig äldre skog med fältskikt dominerat av blåbärs- och lingonris. På frisk-fuktig mark.</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Staffan Åström</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Staffan Åström</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116620214</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>79420805</v>
+      </c>
+      <c r="B26" t="n">
+        <v>109815</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220204</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Slåtterfibbla</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Hypochaeris maculata</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Spikbodarna, 510 m SSV om intill stig, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>485178</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7005053</v>
+      </c>
+      <c r="S26" t="n">
+        <v>25</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2019-08-14</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2019-08-14</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Staffan Åström</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Staffan Åström</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/79420805</t>
         </is>
@@ -3337,6 +3452,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 902-2024 artfynd.xlsx
+++ b/artfynd/S 902-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136950525</v>
       </c>
       <c r="B2" t="n">
-        <v>99355</v>
+        <v>99361</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         <v>112431163</v>
       </c>
       <c r="B15" t="n">
-        <v>89206</v>
+        <v>89208</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/S 902-2024 artfynd.xlsx
+++ b/artfynd/S 902-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136950525</v>
       </c>
       <c r="B2" t="n">
-        <v>99361</v>
+        <v>99363</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         <v>112431163</v>
       </c>
       <c r="B15" t="n">
-        <v>89208</v>
+        <v>89210</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/S 902-2024 artfynd.xlsx
+++ b/artfynd/S 902-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136950525</v>
       </c>
       <c r="B2" t="n">
-        <v>99363</v>
+        <v>99364</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         <v>112431163</v>
       </c>
       <c r="B15" t="n">
-        <v>89210</v>
+        <v>89211</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/S 902-2024 artfynd.xlsx
+++ b/artfynd/S 902-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136950525</v>
       </c>
       <c r="B2" t="n">
-        <v>99364</v>
+        <v>99370</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         <v>112431163</v>
       </c>
       <c r="B15" t="n">
-        <v>89211</v>
+        <v>89217</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/S 902-2024 artfynd.xlsx
+++ b/artfynd/S 902-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136950525</v>
       </c>
       <c r="B2" t="n">
-        <v>99370</v>
+        <v>99374</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         <v>112431163</v>
       </c>
       <c r="B15" t="n">
-        <v>89217</v>
+        <v>89221</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/S 902-2024 artfynd.xlsx
+++ b/artfynd/S 902-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136950525</v>
       </c>
       <c r="B2" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 902-2024 artfynd.xlsx
+++ b/artfynd/S 902-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136950525</v>
       </c>
       <c r="B2" t="n">
-        <v>99376</v>
+        <v>99378</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         <v>112431163</v>
       </c>
       <c r="B15" t="n">
-        <v>89221</v>
+        <v>89223</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/S 902-2024 artfynd.xlsx
+++ b/artfynd/S 902-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136950525</v>
       </c>
       <c r="B2" t="n">
-        <v>99378</v>
+        <v>99391</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         <v>112431163</v>
       </c>
       <c r="B15" t="n">
-        <v>89223</v>
+        <v>89236</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/S 902-2024 artfynd.xlsx
+++ b/artfynd/S 902-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136950525</v>
       </c>
       <c r="B2" t="n">
-        <v>99391</v>
+        <v>99393</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         <v>112431163</v>
       </c>
       <c r="B15" t="n">
-        <v>89236</v>
+        <v>89238</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/S 902-2024 artfynd.xlsx
+++ b/artfynd/S 902-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136950525</v>
       </c>
       <c r="B2" t="n">
-        <v>99393</v>
+        <v>99396</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         <v>112431163</v>
       </c>
       <c r="B15" t="n">
-        <v>89238</v>
+        <v>89241</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/S 902-2024 artfynd.xlsx
+++ b/artfynd/S 902-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136950525</v>
       </c>
       <c r="B2" t="n">
-        <v>99396</v>
+        <v>99406</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         <v>112431163</v>
       </c>
       <c r="B15" t="n">
-        <v>89241</v>
+        <v>89251</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/S 902-2024 artfynd.xlsx
+++ b/artfynd/S 902-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136950525</v>
       </c>
       <c r="B2" t="n">
-        <v>99406</v>
+        <v>99407</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         <v>112431163</v>
       </c>
       <c r="B15" t="n">
-        <v>89251</v>
+        <v>89252</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/S 902-2024 artfynd.xlsx
+++ b/artfynd/S 902-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136950525</v>
       </c>
       <c r="B2" t="n">
-        <v>99407</v>
+        <v>99412</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         <v>112431163</v>
       </c>
       <c r="B15" t="n">
-        <v>89252</v>
+        <v>89255</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/S 902-2024 artfynd.xlsx
+++ b/artfynd/S 902-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136950525</v>
       </c>
       <c r="B2" t="n">
-        <v>99412</v>
+        <v>99414</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 902-2024 artfynd.xlsx
+++ b/artfynd/S 902-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136950525</v>
       </c>
       <c r="B2" t="n">
-        <v>99414</v>
+        <v>99420</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         <v>112431163</v>
       </c>
       <c r="B15" t="n">
-        <v>89255</v>
+        <v>89260</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/S 902-2024 artfynd.xlsx
+++ b/artfynd/S 902-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136950525</v>
       </c>
       <c r="B2" t="n">
-        <v>99420</v>
+        <v>99432</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         <v>112431163</v>
       </c>
       <c r="B15" t="n">
-        <v>89260</v>
+        <v>89271</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/S 902-2024 artfynd.xlsx
+++ b/artfynd/S 902-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136950525</v>
       </c>
       <c r="B2" t="n">
-        <v>99432</v>
+        <v>99433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         <v>112431163</v>
       </c>
       <c r="B15" t="n">
-        <v>89271</v>
+        <v>89272</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/S 902-2024 artfynd.xlsx
+++ b/artfynd/S 902-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136950525</v>
       </c>
       <c r="B2" t="n">
-        <v>99433</v>
+        <v>99436</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         <v>112431163</v>
       </c>
       <c r="B15" t="n">
-        <v>89272</v>
+        <v>89275</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/S 902-2024 artfynd.xlsx
+++ b/artfynd/S 902-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136950525</v>
       </c>
       <c r="B2" t="n">
-        <v>99436</v>
+        <v>99437</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 902-2024 artfynd.xlsx
+++ b/artfynd/S 902-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136950525</v>
       </c>
       <c r="B2" t="n">
-        <v>99437</v>
+        <v>99440</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
